--- a/results/final_20260514_v2_summary/CHD_49_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/CHD_49_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.5787±0.0193</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5863±0.0384</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5648±0.0610</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.4605±0.0890</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.7348±0.0137</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.7381±0.0161</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.7621±0.0208</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.7855±0.0190</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.6604±0.0273</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.6519±0.0260</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.6420±0.0316</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6097±0.0321</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.7318±0.0280</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.7331±0.0297</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.6997±0.0485</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6461±0.0418</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.6711±0.0215</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.6660±0.0228</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.6434±0.0341</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.6013±0.0315</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.7211±0.0131</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.7126±0.0171</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.7024±0.0247</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.6697±0.0236</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5723±0.0248</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5656±0.0261</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5491±0.0375</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5159±0.0313</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5318±0.0099</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5185±0.0202</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5018±0.0346</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.4982±0.0340</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5102±0.0098</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4973±0.0209</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.4845±0.0328</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.4737±0.0377</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5740±0.0220</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5651±0.0291</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.5421±0.0460</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.5371±0.0380</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9985±0.0034</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9888±0.0098</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9178±0.0785</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.6992±0.0180</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6902±0.0220</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.6761±0.0319</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.6422±0.0257</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.6539±0.0240</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.6422±0.0245</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.6339±0.0314</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.6014±0.0304</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.7523±0.0269</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7468±0.0304</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.7259±0.0463</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6904±0.0353</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.2414±0.0293</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.2396±0.0352</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.2605±0.0494</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.2919±0.0408</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.2414±0.0293</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.2396±0.0352</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.2520±0.0474</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.2524±0.0348</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.5753±0.0204</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.5838±0.0373</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.5635±0.0566</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.4632±0.0859</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.7357±0.0154</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.7369±0.0168</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.7619±0.0209</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.7834±0.0192</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6577±0.0291</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6460±0.0263</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6361±0.0308</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6059±0.0332</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7550±0.0306</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.7511±0.0295</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.7184±0.0462</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6541±0.0419</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.6787±0.0241</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.6701±0.0234</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.6486±0.0331</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6028±0.0322</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.7219±0.0143</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.7112±0.0173</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.7022±0.0243</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6668±0.0245</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.5778±0.0292</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.5684±0.0268</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.5527±0.0367</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.5163±0.0320</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.5408±0.0129</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.5269±0.0196</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.5107±0.0320</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.5007±0.0345</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.5088±0.0142</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.4939±0.0193</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.4828±0.0299</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.4708±0.0379</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.5945±0.0229</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.5853±0.0297</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.5618±0.0439</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.5461±0.0387</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9985±0.0034</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9896±0.0108</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9155±0.0818</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.7054±0.0216</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6944±0.0227</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6816±0.0307</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6432±0.0266</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6498±0.0273</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6361±0.0254</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6291±0.0298</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.5961±0.0315</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7725±0.0296</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7655±0.0310</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7451±0.0449</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6999±0.0352</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.2360±0.0392</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.2346±0.0402</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.2566±0.0514</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.2886±0.0410</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.2360±0.0392</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.2346±0.0402</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.2481±0.0487</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.2489±0.0361</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.5754±0.0157</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.5847±0.0429</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5638±0.0621</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.4603±0.0869</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.7351±0.0128</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.7386±0.0174</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.7629±0.0204</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.7855±0.0185</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.6608±0.0255</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.6521±0.0268</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.6422±0.0312</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.6095±0.0315</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.7322±0.0276</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.7337±0.0303</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.7003±0.0476</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.6456±0.0413</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.6716±0.0198</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.6663±0.0235</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.6440±0.0338</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.6009±0.0306</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.7213±0.0124</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.7130±0.0184</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.7034±0.0242</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.6696±0.0228</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5732±0.0225</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5661±0.0269</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.5498±0.0370</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.5154±0.0303</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.5323±0.0094</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.5194±0.0222</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.5033±0.0338</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.4986±0.0331</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5104±0.0084</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.4984±0.0220</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.4859±0.0320</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.4739±0.0370</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5744±0.0225</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5660±0.0306</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5436±0.0445</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5374±0.0372</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9985±0.0034</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9884±0.0103</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9181±0.0769</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6995±0.0166</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6907±0.0231</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.6771±0.0317</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.6421±0.0249</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6544±0.0227</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.6427±0.0257</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.6349±0.0316</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.6014±0.0298</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.7523±0.0266</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.7473±0.0312</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.7268±0.0452</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.6903±0.0353</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.2468±0.0271</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.2404±0.0365</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.2613±0.0499</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.2915±0.0400</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.2468±0.0271</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.2404±0.0365</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.2528±0.0477</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.2520±0.0338</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.5758±0.0193</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5825±0.0403</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.5623±0.0565</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.4630±0.0831</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.7357±0.0141</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.7369±0.0178</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.7618±0.0207</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.7834±0.0192</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.6580±0.0271</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.6457±0.0273</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.6361±0.0297</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.6058±0.0334</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.7555±0.0301</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.7522±0.0306</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.7199±0.0446</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.6544±0.0413</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.6790±0.0222</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.6703±0.0245</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.6490±0.0320</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.6030±0.0317</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.7218±0.0132</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.7113±0.0185</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.7023±0.0240</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6669±0.0240</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.5784±0.0267</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.5683±0.0279</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.5527±0.0360</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.5167±0.0313</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.5408±0.0120</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.5275±0.0210</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.5113±0.0316</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.5012±0.0330</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.5091±0.0126</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.4941±0.0202</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.4827±0.0296</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.4712±0.0362</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.5946±0.0228</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.5864±0.0308</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.5628±0.0436</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.5467±0.0376</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9985±0.0034</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9896±0.0108</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9155±0.0818</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.7054±0.0201</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.6946±0.0239</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.6819±0.0305</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.6435±0.0259</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.6498±0.0258</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.6359±0.0267</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.6289±0.0297</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.5962±0.0314</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.7726±0.0291</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.7663±0.0319</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.7461±0.0445</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.7006±0.0344</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.2378±0.0359</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.2335±0.0404</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.2559±0.0523</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.2894±0.0408</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.2378±0.0359</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.2335±0.0404</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.2474±0.0494</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.2497±0.0354</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.6373±0.0441</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.6194±0.0548</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.5911±0.0636</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.4537±0.0770</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.7189±0.0243</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.7017±0.0213</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.6878±0.0161</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.6587±0.0180</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.6859±0.0402</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.6685±0.0255</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.6541±0.0302</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.6111±0.0254</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.6571±0.0351</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.6222±0.0387</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5830±0.0315</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.5587±0.0315</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.6452±0.0311</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.6186±0.0270</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.5891±0.0231</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.5558±0.0205</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.7183±0.0246</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.7011±0.0213</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.6847±0.0165</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.6514±0.0180</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.5357±0.0336</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.5064±0.0286</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.4751±0.0239</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.4370±0.0215</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.4856±0.0263</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.4646±0.0253</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.4452±0.0269</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.4455±0.0258</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.5289±0.0248</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.5075±0.0169</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.4921±0.0271</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.4699±0.0234</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.4845±0.0243</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.4602±0.0256</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.4340±0.0284</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.4355±0.0280</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9985±0.0034</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9921±0.0073</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.9338±0.0800</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.6665±0.0301</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.6421±0.0262</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.6174±0.0214</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.5828±0.0197</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.6794±0.0392</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.6619±0.0255</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.6471±0.0278</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.6026±0.0258</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.6556±0.0343</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.6243±0.0347</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.5914±0.0302</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.5652±0.0272</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.1802±0.0273</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.1506±0.0313</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.1261±0.0247</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.0868±0.0267</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.1802±0.0273</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.1506±0.0313</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.1249±0.0244</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0852±0.0264</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.5550±0.0279</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.5550±0.0464</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.5453±0.0458</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.4796±0.0475</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.7144±0.0114</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.6939±0.0174</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.6804±0.0167</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.6474±0.0154</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.6486±0.0238</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.6238±0.0246</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.6046±0.0275</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.5716±0.0236</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.7654±0.0270</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.7563±0.0326</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.7554±0.0319</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.7421±0.0261</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.6761±0.0187</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.6570±0.0235</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.6442±0.0214</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.6161±0.0163</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.7132±0.0109</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.6927±0.0175</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.6767±0.0160</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.6393±0.0155</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.5687±0.0232</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.5431±0.0252</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.5256±0.0230</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.4914±0.0181</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.5424±0.0092</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.5306±0.0190</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.5228±0.0169</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.5159±0.0207</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.5031±0.0120</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.4877±0.0304</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.4704±0.0199</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.4561±0.0228</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.6019±0.0189</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.5981±0.0252</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.5990±0.0256</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.6042±0.0317</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9948±0.0083</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9799±0.0169</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8933±0.0652</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.6989±0.0172</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.6822±0.0230</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.6712±0.0199</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.6427±0.0157</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.6374±0.0239</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.6142±0.0258</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.5978±0.0258</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.5620±0.0231</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.7747±0.0264</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.7681±0.0308</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7664±0.0287</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.7520±0.0249</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.1946±0.0472</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.1571±0.0336</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.1254±0.0345</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0883±0.0219</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.1946±0.0472</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.1571±0.0336</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.1242±0.0342</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0863±0.0221</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.6566±0.0546</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.6371±0.0446</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.5878±0.0559</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.4456±0.0697</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.7063±0.0238</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.6948±0.0231</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.6823±0.0171</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.6511±0.0173</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.6841±0.0431</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.6739±0.0282</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.6577±0.0349</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.6081±0.0247</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.6081±0.0356</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5815±0.0396</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5483±0.0322</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.5317±0.0311</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.6189±0.0352</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.5977±0.0295</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.5700±0.0260</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.5386±0.0217</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.7056±0.0240</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.6941±0.0231</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.6790±0.0171</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.6440±0.0171</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5059±0.0373</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4844±0.0312</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.4552±0.0267</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.4192±0.0214</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.4508±0.0322</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.4396±0.0254</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.4276±0.0277</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.4316±0.0236</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.5208±0.0335</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.5070±0.0201</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.4911±0.0298</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.4677±0.0205</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4411±0.0224</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.4230±0.0237</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.4050±0.0273</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.4123±0.0260</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9989±0.0030</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9918±0.0081</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.9340±0.0734</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.6377±0.0330</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.6199±0.0292</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.5976±0.0233</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.5646±0.0199</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.6767±0.0415</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.6654±0.0275</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.6500±0.0302</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.5981±0.0247</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.6038±0.0332</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.5810±0.0359</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.5541±0.0295</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.5355±0.0266</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.1550±0.0319</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.1398±0.0319</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.1150±0.0333</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.0775±0.0242</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.1550±0.0319</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.1398±0.0319</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.1137±0.0329</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0768±0.0240</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.5540±0.0273</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.5565±0.0475</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.5421±0.0433</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.4790±0.0489</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.7159±0.0131</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.6926±0.0167</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.6810±0.0173</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.6468±0.0149</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.6500±0.0261</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.6225±0.0244</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.6051±0.0276</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.5708±0.0238</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.7663±0.0259</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.7551±0.0317</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.7566±0.0330</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.7386±0.0242</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.6773±0.0200</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.6557±0.0235</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.6451±0.0220</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.6144±0.0158</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.7148±0.0127</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.6914±0.0168</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.6772±0.0167</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.6385±0.0150</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.5701±0.0245</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.5418±0.0253</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.5267±0.0239</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.4895±0.0178</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.5441±0.0110</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.5296±0.0197</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.5258±0.0195</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.5147±0.0208</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.5055±0.0157</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.4862±0.0312</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.4740±0.0248</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.4557±0.0228</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.6030±0.0183</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.5977±0.0258</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.6020±0.0284</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.6016±0.0317</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9948±0.0091</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9813±0.0128</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8927±0.0671</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.7004±0.0184</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.6811±0.0232</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.6720±0.0207</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.6414±0.0151</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.6393±0.0262</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.6128±0.0258</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.5982±0.0265</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.5617±0.0230</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.7755±0.0253</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.7677±0.0316</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.7679±0.0294</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.7491±0.0245</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.1964±0.0485</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.1553±0.0331</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.1276±0.0345</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0868±0.0228</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.1964±0.0485</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.1553±0.0331</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.1260±0.0340</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0845±0.0230</t>
         </is>
